--- a/outputs/Estadistica Ejercicio/Municipios 911.xlsx
+++ b/outputs/Estadistica Ejercicio/Municipios 911.xlsx
@@ -1070,10 +1070,10 @@
         <v>38</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>47</v>
@@ -1145,10 +1145,10 @@
         <v>0.1706</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0404</v>
+        <v>0.0045</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1302</v>
+        <v>0.1662</v>
       </c>
       <c r="AF2" t="n">
         <v>0.2111</v>
@@ -1220,10 +1220,10 @@
         <v>1.7065</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4042</v>
+        <v>0.0449</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.3023</v>
+        <v>1.6616</v>
       </c>
       <c r="BE2" t="n">
         <v>2.1107</v>
@@ -1303,10 +1303,10 @@
         <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -1378,10 +1378,10 @@
         <v>0.1259</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0369</v>
+        <v>0.0022</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0977</v>
+        <v>0.1324</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1129</v>
@@ -1453,10 +1453,10 @@
         <v>1.2591</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.369</v>
+        <v>0.0217</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.9769</v>
+        <v>1.3242</v>
       </c>
       <c r="BE3" t="n">
         <v>1.1288</v>
@@ -1536,10 +1536,10 @@
         <v>150</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>351</v>
+        <v>463</v>
       </c>
       <c r="G4" t="n">
         <v>228</v>
@@ -1611,10 +1611,10 @@
         <v>0.2459</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2606</v>
+        <v>0.077</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5754</v>
+        <v>0.759</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3738</v>
@@ -1686,10 +1686,10 @@
         <v>2.4589</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.6065</v>
+        <v>0.7705</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7539</v>
+        <v>7.5899</v>
       </c>
       <c r="BE4" t="n">
         <v>3.7376</v>
@@ -1769,10 +1769,10 @@
         <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1844,10 +1844,10 @@
         <v>0.4073</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0679</v>
+        <v>0.0194</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1358</v>
+        <v>0.1842</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1939</v>
@@ -1919,10 +1919,10 @@
         <v>4.0725</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.6788</v>
+        <v>0.1939</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.3575</v>
+        <v>1.8423</v>
       </c>
       <c r="BE5" t="n">
         <v>1.9393</v>
@@ -2002,10 +2002,10 @@
         <v>131</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
         <v>64</v>
@@ -2077,10 +2077,10 @@
         <v>0.6942</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1484</v>
+        <v>0.0424</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3391</v>
+        <v>0.4451</v>
       </c>
       <c r="AF6" t="n">
         <v>0.3391</v>
@@ -2152,10 +2152,10 @@
         <v>6.9415</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.4837</v>
+        <v>0.4239</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3913</v>
+        <v>4.451</v>
       </c>
       <c r="BE6" t="n">
         <v>3.3913</v>
@@ -2235,10 +2235,10 @@
         <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -2310,10 +2310,10 @@
         <v>0.2087</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0104</v>
+        <v>0.0052</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0365</v>
+        <v>0.0417</v>
       </c>
       <c r="AF7" t="n">
         <v>0.0313</v>
@@ -2385,10 +2385,10 @@
         <v>2.0875</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1044</v>
+        <v>0.0522</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.3653</v>
+        <v>0.4175</v>
       </c>
       <c r="BE7" t="n">
         <v>0.3131</v>
@@ -2468,10 +2468,10 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
         <v>17</v>
@@ -2543,10 +2543,10 @@
         <v>0.0239</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2311</v>
+        <v>0.0638</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1833</v>
+        <v>0.3507</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1355</v>
@@ -2618,10 +2618,10 @@
         <v>0.2391</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.3115</v>
+        <v>0.6377</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.8333</v>
+        <v>3.5071</v>
       </c>
       <c r="BE8" t="n">
         <v>1.355</v>
@@ -2701,10 +2701,10 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>210</v>
+        <v>314</v>
       </c>
       <c r="G9" t="n">
         <v>174</v>
@@ -2776,10 +2776,10 @@
         <v>0.0493</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3278</v>
+        <v>0.105</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4499</v>
+        <v>0.6727</v>
       </c>
       <c r="AF9" t="n">
         <v>0.3727</v>
@@ -2851,10 +2851,10 @@
         <v>0.4927</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.2776</v>
+        <v>1.0497</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4986</v>
+        <v>6.7265</v>
       </c>
       <c r="BE9" t="n">
         <v>3.7274</v>
@@ -2934,10 +2934,10 @@
         <v>153</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="G10" t="n">
         <v>148</v>
@@ -3009,10 +3009,10 @@
         <v>0.4853</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2062</v>
+        <v>0.0666</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4377</v>
+        <v>0.5773</v>
       </c>
       <c r="AF10" t="n">
         <v>0.4695</v>
@@ -3084,10 +3084,10 @@
         <v>4.8533</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.0619</v>
+        <v>0.6661</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3775</v>
+        <v>5.7732</v>
       </c>
       <c r="BE10" t="n">
         <v>4.6947</v>
@@ -3167,10 +3167,10 @@
         <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
@@ -3242,10 +3242,10 @@
         <v>0.3432</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0353</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0454</v>
+        <v>0.0808</v>
       </c>
       <c r="AF11" t="n">
         <v>0.0151</v>
@@ -3317,10 +3317,10 @@
         <v>3.4323</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.3533</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.4543</v>
+        <v>0.8076</v>
       </c>
       <c r="BE11" t="n">
         <v>0.1514</v>
@@ -3400,10 +3400,10 @@
         <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>363</v>
+        <v>437</v>
       </c>
       <c r="G12" t="n">
         <v>200</v>
@@ -3475,10 +3475,10 @@
         <v>0.1265</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1617</v>
+        <v>0.0432</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5811</v>
+        <v>0.6995</v>
       </c>
       <c r="AF12" t="n">
         <v>0.3202</v>
@@ -3550,10 +3550,10 @@
         <v>1.2646</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.6168</v>
+        <v>0.4322</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8108</v>
+        <v>6.9954</v>
       </c>
       <c r="BE12" t="n">
         <v>3.2015</v>
@@ -3633,10 +3633,10 @@
         <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
         <v>39</v>
@@ -3708,10 +3708,10 @@
         <v>0.2489</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1095</v>
+        <v>0.0465</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.146</v>
+        <v>0.2091</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1294</v>
@@ -3783,10 +3783,10 @@
         <v>2.4888</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.0951</v>
+        <v>0.4646</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.4601</v>
+        <v>2.0906</v>
       </c>
       <c r="BE13" t="n">
         <v>1.2942</v>
@@ -4099,10 +4099,10 @@
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -4174,10 +4174,10 @@
         <v>0.3602</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0103</v>
+        <v>0.0154</v>
       </c>
       <c r="AF15" t="n">
         <v>0.0051</v>
@@ -4249,10 +4249,10 @@
         <v>3.6025</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.1029</v>
+        <v>0.1544</v>
       </c>
       <c r="BE15" t="n">
         <v>0.0515</v>
@@ -4332,10 +4332,10 @@
         <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>21</v>
@@ -4407,10 +4407,10 @@
         <v>0.1003</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0386</v>
+        <v>0.0154</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3085</v>
+        <v>0.3316</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1619</v>
@@ -4482,10 +4482,10 @@
         <v>1.0025</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.3856</v>
+        <v>0.1542</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.0848</v>
+        <v>3.3161</v>
       </c>
       <c r="BE16" t="n">
         <v>1.6195</v>
@@ -4565,10 +4565,10 @@
         <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -4640,10 +4640,10 @@
         <v>0.2139</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0175</v>
+        <v>0.0306</v>
       </c>
       <c r="AF17" t="n">
         <v>0.0175</v>
@@ -4715,10 +4715,10 @@
         <v>2.1395</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.1746</v>
+        <v>0.3056</v>
       </c>
       <c r="BE17" t="n">
         <v>0.1746</v>
@@ -4798,10 +4798,10 @@
         <v>150</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
         <v>11</v>
@@ -4873,10 +4873,10 @@
         <v>0.7933</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0264</v>
+        <v>0.0106</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0635</v>
+        <v>0.0793</v>
       </c>
       <c r="AF18" t="n">
         <v>0.0582</v>
@@ -4948,10 +4948,10 @@
         <v>7.9327</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.2644</v>
+        <v>0.1058</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.6346</v>
+        <v>0.7933</v>
       </c>
       <c r="BE18" t="n">
         <v>0.5817</v>
@@ -5031,10 +5031,10 @@
         <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="G19" t="n">
         <v>155</v>
@@ -5106,10 +5106,10 @@
         <v>0.1225</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1572</v>
+        <v>0.0397</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2234</v>
+        <v>0.3409</v>
       </c>
       <c r="AF19" t="n">
         <v>0.2565</v>
@@ -5181,10 +5181,10 @@
         <v>1.2247</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.5723</v>
+        <v>0.3972</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.2343</v>
+        <v>3.4094</v>
       </c>
       <c r="BE19" t="n">
         <v>2.5653</v>
@@ -5264,10 +5264,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G20" t="n">
         <v>52</v>
@@ -5339,10 +5339,10 @@
         <v>0.1311</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0857</v>
+        <v>0.0252</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.2974</v>
+        <v>0.3579</v>
       </c>
       <c r="AF20" t="n">
         <v>0.2621</v>
@@ -5414,10 +5414,10 @@
         <v>1.3107</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.857</v>
+        <v>0.2521</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.9744</v>
+        <v>3.5794</v>
       </c>
       <c r="BE20" t="n">
         <v>2.6215</v>
@@ -5730,10 +5730,10 @@
         <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
         <v>39</v>
@@ -5805,10 +5805,10 @@
         <v>0.0791</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.0857</v>
+        <v>0.0329</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.257</v>
+        <v>0.3097</v>
       </c>
       <c r="AF22" t="n">
         <v>0.257</v>
@@ -5880,10 +5880,10 @@
         <v>0.7908</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.8567</v>
+        <v>0.3295</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.57</v>
+        <v>3.0972</v>
       </c>
       <c r="BE22" t="n">
         <v>2.57</v>
@@ -5963,10 +5963,10 @@
         <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
         <v>79</v>
@@ -6038,10 +6038,10 @@
         <v>0.1842</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1474</v>
+        <v>0.043</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.5404</v>
+        <v>0.6448</v>
       </c>
       <c r="AF23" t="n">
         <v>0.4851</v>
@@ -6113,10 +6113,10 @@
         <v>1.8422</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.4737</v>
+        <v>0.4298</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.4037</v>
+        <v>6.4477</v>
       </c>
       <c r="BE23" t="n">
         <v>4.8511</v>
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G24" t="n">
         <v>67</v>
@@ -6271,10 +6271,10 @@
         <v>0.0635</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.091</v>
+        <v>0.0331</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3062</v>
+        <v>0.3642</v>
       </c>
       <c r="AF24" t="n">
         <v>0.1848</v>
@@ -6346,10 +6346,10 @@
         <v>0.6345</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.9104</v>
+        <v>0.3311</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.0622</v>
+        <v>3.6416</v>
       </c>
       <c r="BE24" t="n">
         <v>1.8484</v>
@@ -6429,10 +6429,10 @@
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
         <v>18</v>
@@ -6504,10 +6504,10 @@
         <v>0.0682</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.0454</v>
+        <v>0.017</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.142</v>
+        <v>0.1704</v>
       </c>
       <c r="AF25" t="n">
         <v>0.1022</v>
@@ -6579,10 +6579,10 @@
         <v>0.6815</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.4544</v>
+        <v>0.1704</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.4199</v>
+        <v>1.7039</v>
       </c>
       <c r="BE25" t="n">
         <v>1.0223</v>
@@ -6662,10 +6662,10 @@
         <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -6737,10 +6737,10 @@
         <v>0.0919</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0097</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0097</v>
+        <v>0.0193</v>
       </c>
       <c r="AF26" t="n">
         <v>0.0097</v>
@@ -6812,10 +6812,10 @@
         <v>0.9191</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.0967</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>0.0967</v>
+        <v>0.1935</v>
       </c>
       <c r="BE26" t="n">
         <v>0.0967</v>
@@ -7128,10 +7128,10 @@
         <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -7203,10 +7203,10 @@
         <v>0.3458</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0088</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0044</v>
+        <v>0.0131</v>
       </c>
       <c r="AF28" t="n">
         <v>0.0044</v>
@@ -7278,10 +7278,10 @@
         <v>3.4579</v>
       </c>
       <c r="BC28" t="n">
-        <v>0.0875</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>0.0438</v>
+        <v>0.1313</v>
       </c>
       <c r="BE28" t="n">
         <v>0.0438</v>
@@ -7361,10 +7361,10 @@
         <v>148</v>
       </c>
       <c r="E29" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="G29" t="n">
         <v>100</v>
@@ -7436,10 +7436,10 @@
         <v>0.1167</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0805</v>
+        <v>0.015</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1522</v>
+        <v>0.2177</v>
       </c>
       <c r="AF29" t="n">
         <v>0.0789</v>
@@ -7511,10 +7511,10 @@
         <v>1.1674</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.8045</v>
+        <v>0.1499</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.5223</v>
+        <v>2.177</v>
       </c>
       <c r="BE29" t="n">
         <v>0.7888</v>
@@ -7594,10 +7594,10 @@
         <v>166</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="G30" t="n">
         <v>99</v>
@@ -7669,10 +7669,10 @@
         <v>0.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0886</v>
+        <v>0.0232</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1919</v>
+        <v>0.2572</v>
       </c>
       <c r="AF30" t="n">
         <v>0.2088</v>
@@ -7744,10 +7744,10 @@
         <v>3.5003</v>
       </c>
       <c r="BC30" t="n">
-        <v>0.8856</v>
+        <v>0.2319</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.9188</v>
+        <v>2.5725</v>
       </c>
       <c r="BE30" t="n">
         <v>2.0875</v>
@@ -7827,10 +7827,10 @@
         <v>144</v>
       </c>
       <c r="E31" t="n">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>247</v>
+        <v>344</v>
       </c>
       <c r="G31" t="n">
         <v>130</v>
@@ -7902,10 +7902,10 @@
         <v>0.146</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.1379</v>
+        <v>0.0395</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2504</v>
+        <v>0.3487</v>
       </c>
       <c r="AF31" t="n">
         <v>0.1318</v>
@@ -7977,10 +7977,10 @@
         <v>1.4596</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.3786</v>
+        <v>0.3953</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.5037</v>
+        <v>3.4869</v>
       </c>
       <c r="BE31" t="n">
         <v>1.3177</v>
@@ -8060,10 +8060,10 @@
         <v>22</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>8</v>
@@ -8135,10 +8135,10 @@
         <v>0.179</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0488</v>
+        <v>0.0081</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0732</v>
+        <v>0.1139</v>
       </c>
       <c r="AF32" t="n">
         <v>0.0651</v>
@@ -8210,10 +8210,10 @@
         <v>1.7901</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.4882</v>
+        <v>0.0814</v>
       </c>
       <c r="BD32" t="n">
-        <v>0.7323</v>
+        <v>1.1391</v>
       </c>
       <c r="BE32" t="n">
         <v>0.6509</v>
@@ -8293,10 +8293,10 @@
         <v>92</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -8368,10 +8368,10 @@
         <v>0.8743</v>
       </c>
       <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
         <v>0.0095</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0.0095</v>
@@ -8443,10 +8443,10 @@
         <v>8.7428</v>
       </c>
       <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
         <v>0.095</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
       </c>
       <c r="BE33" t="n">
         <v>0.095</v>
@@ -8759,10 +8759,10 @@
         <v>18</v>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -8834,10 +8834,10 @@
         <v>0.1833</v>
       </c>
       <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
         <v>0.0102</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0.0102</v>
@@ -8909,10 +8909,10 @@
         <v>1.8332</v>
       </c>
       <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
         <v>0.1018</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
       </c>
       <c r="BE35" t="n">
         <v>0.1018</v>
@@ -9225,10 +9225,10 @@
         <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
         <v>15</v>
@@ -9300,10 +9300,10 @@
         <v>0.3059</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.0306</v>
+        <v>0.0153</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.0459</v>
+        <v>0.0612</v>
       </c>
       <c r="AF37" t="n">
         <v>0.1147</v>
@@ -9375,10 +9375,10 @@
         <v>3.0586</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.3059</v>
+        <v>0.1529</v>
       </c>
       <c r="BD37" t="n">
-        <v>0.4588</v>
+        <v>0.6117</v>
       </c>
       <c r="BE37" t="n">
         <v>1.147</v>
@@ -9458,10 +9458,10 @@
         <v>136</v>
       </c>
       <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
         <v>7</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>8</v>
@@ -9533,10 +9533,10 @@
         <v>0.6488</v>
       </c>
       <c r="AD38" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.0334</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.0143</v>
       </c>
       <c r="AF38" t="n">
         <v>0.0382</v>
@@ -9608,10 +9608,10 @@
         <v>6.4879</v>
       </c>
       <c r="BC38" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="BD38" t="n">
         <v>0.3339</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0.1431</v>
       </c>
       <c r="BE38" t="n">
         <v>0.3816</v>
@@ -9691,10 +9691,10 @@
         <v>234</v>
       </c>
       <c r="E39" t="n">
-        <v>1133</v>
+        <v>375</v>
       </c>
       <c r="F39" t="n">
-        <v>2324</v>
+        <v>3082</v>
       </c>
       <c r="G39" t="n">
         <v>1720</v>
@@ -9766,10 +9766,10 @@
         <v>0.1154</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.5588</v>
+        <v>0.185</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.1462</v>
+        <v>1.5201</v>
       </c>
       <c r="AF39" t="n">
         <v>0.8483</v>
@@ -9841,10 +9841,10 @@
         <v>1.1541</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.5882</v>
+        <v>1.8496</v>
       </c>
       <c r="BD39" t="n">
-        <v>11.4624</v>
+        <v>15.2011</v>
       </c>
       <c r="BE39" t="n">
         <v>8.4834</v>
@@ -10157,10 +10157,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G41" t="n">
         <v>34</v>
@@ -10232,10 +10232,10 @@
         <v>0.007</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.1466</v>
+        <v>0.0698</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.4468</v>
+        <v>0.5236</v>
       </c>
       <c r="AF41" t="n">
         <v>0.2374</v>
@@ -10307,10 +10307,10 @@
         <v>0.0698</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.4661</v>
+        <v>0.6981</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.468</v>
+        <v>5.236</v>
       </c>
       <c r="BE41" t="n">
         <v>2.3736</v>
@@ -10390,10 +10390,10 @@
         <v>58</v>
       </c>
       <c r="E42" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F42" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="G42" t="n">
         <v>98</v>
@@ -10465,10 +10465,10 @@
         <v>0.1228</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.1927</v>
+        <v>0.0466</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.3176</v>
+        <v>0.4638</v>
       </c>
       <c r="AF42" t="n">
         <v>0.2075</v>
@@ -10540,10 +10540,10 @@
         <v>1.2282</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.9271</v>
+        <v>0.4659</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.1765</v>
+        <v>4.6377</v>
       </c>
       <c r="BE42" t="n">
         <v>2.0753</v>
@@ -10623,10 +10623,10 @@
         <v>172</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
         <v>3</v>
@@ -10698,10 +10698,10 @@
         <v>1.4856</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.0173</v>
+        <v>0.0086</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.0518</v>
+        <v>0.0605</v>
       </c>
       <c r="AF43" t="n">
         <v>0.0259</v>
@@ -10773,10 +10773,10 @@
         <v>14.8558</v>
       </c>
       <c r="BC43" t="n">
-        <v>0.1727</v>
+        <v>0.0864</v>
       </c>
       <c r="BD43" t="n">
-        <v>0.5182</v>
+        <v>0.6046</v>
       </c>
       <c r="BE43" t="n">
         <v>0.2591</v>
@@ -11089,10 +11089,10 @@
         <v>22</v>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
         <v>32</v>
@@ -11164,10 +11164,10 @@
         <v>0.1298</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.0472</v>
+        <v>0.0059</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.1003</v>
+        <v>0.1416</v>
       </c>
       <c r="AF45" t="n">
         <v>0.1888</v>
@@ -11239,10 +11239,10 @@
         <v>1.2981</v>
       </c>
       <c r="BC45" t="n">
-        <v>0.472</v>
+        <v>0.059</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.0031</v>
+        <v>1.4161</v>
       </c>
       <c r="BE45" t="n">
         <v>1.8881</v>
@@ -11322,10 +11322,10 @@
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
         <v>30</v>
@@ -11397,10 +11397,10 @@
         <v>0.043</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.0646</v>
+        <v>0.043</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.1614</v>
+        <v>0.1829</v>
       </c>
       <c r="AF46" t="n">
         <v>0.3228</v>
@@ -11472,10 +11472,10 @@
         <v>0.4303</v>
       </c>
       <c r="BC46" t="n">
-        <v>0.6455</v>
+        <v>0.4303</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.6138</v>
+        <v>1.8289</v>
       </c>
       <c r="BE46" t="n">
         <v>3.2275</v>
@@ -11555,10 +11555,10 @@
         <v>3051</v>
       </c>
       <c r="E47" t="n">
-        <v>3247</v>
+        <v>1021</v>
       </c>
       <c r="F47" t="n">
-        <v>5292</v>
+        <v>7518</v>
       </c>
       <c r="G47" t="n">
         <v>4118</v>
@@ -11630,10 +11630,10 @@
         <v>0.9706</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.033</v>
+        <v>0.3248</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.6836</v>
+        <v>2.3917</v>
       </c>
       <c r="AF47" t="n">
         <v>1.3101</v>
@@ -11705,10 +11705,10 @@
         <v>9.7063</v>
       </c>
       <c r="BC47" t="n">
-        <v>10.3299</v>
+        <v>3.2482</v>
       </c>
       <c r="BD47" t="n">
-        <v>16.8358</v>
+        <v>23.9175</v>
       </c>
       <c r="BE47" t="n">
         <v>13.1008</v>
@@ -12254,10 +12254,10 @@
         <v>55</v>
       </c>
       <c r="E50" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
         <v>70</v>
@@ -12329,10 +12329,10 @@
         <v>0.2326</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.1819</v>
+        <v>0.055</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.2961</v>
+        <v>0.423</v>
       </c>
       <c r="AF50" t="n">
         <v>0.2961</v>
@@ -12404,10 +12404,10 @@
         <v>2.3265</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.8189</v>
+        <v>0.5499</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.961</v>
+        <v>4.2299</v>
       </c>
       <c r="BE50" t="n">
         <v>2.961</v>
@@ -12487,10 +12487,10 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
         <v>4</v>
@@ -12562,10 +12562,10 @@
         <v>0.0952</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.0423</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.0212</v>
+        <v>0.0635</v>
       </c>
       <c r="AF51" t="n">
         <v>0.0423</v>
@@ -12637,10 +12637,10 @@
         <v>0.9525</v>
       </c>
       <c r="BC51" t="n">
-        <v>0.4233</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>0.2117</v>
+        <v>0.635</v>
       </c>
       <c r="BE51" t="n">
         <v>0.4233</v>
@@ -12720,10 +12720,10 @@
         <v>78</v>
       </c>
       <c r="E52" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="F52" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="G52" t="n">
         <v>135</v>
@@ -12795,10 +12795,10 @@
         <v>0.2006</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.1826</v>
+        <v>0.0566</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.3471</v>
+        <v>0.4731</v>
       </c>
       <c r="AF52" t="n">
         <v>0.3471</v>
@@ -12870,10 +12870,10 @@
         <v>2.0056</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.8256</v>
+        <v>0.5657</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.4712</v>
+        <v>4.7312</v>
       </c>
       <c r="BE52" t="n">
         <v>3.4712</v>
@@ -12953,10 +12953,10 @@
         <v>24</v>
       </c>
       <c r="E53" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G53" t="n">
         <v>12</v>
@@ -13028,10 +13028,10 @@
         <v>0.1356</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.0904</v>
+        <v>0.0396</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.1243</v>
+        <v>0.1752</v>
       </c>
       <c r="AF53" t="n">
         <v>0.0678</v>
@@ -13103,10 +13103,10 @@
         <v>1.356</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.904</v>
+        <v>0.3955</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.243</v>
+        <v>1.7515</v>
       </c>
       <c r="BE53" t="n">
         <v>0.678</v>
@@ -13186,10 +13186,10 @@
         <v>166</v>
       </c>
       <c r="E54" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G54" t="n">
         <v>6</v>
@@ -13261,10 +13261,10 @@
         <v>0.4313</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.0572</v>
+        <v>0.0208</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.0234</v>
+        <v>0.0598</v>
       </c>
       <c r="AF54" t="n">
         <v>0.0156</v>
@@ -13336,10 +13336,10 @@
         <v>4.3126</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.5715</v>
+        <v>0.2078</v>
       </c>
       <c r="BD54" t="n">
-        <v>0.2338</v>
+        <v>0.5975</v>
       </c>
       <c r="BE54" t="n">
         <v>0.1559</v>
@@ -13419,10 +13419,10 @@
         <v>78</v>
       </c>
       <c r="E55" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="G55" t="n">
         <v>64</v>
@@ -13494,10 +13494,10 @@
         <v>0.212</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.106</v>
+        <v>0.0272</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.2256</v>
+        <v>0.3044</v>
       </c>
       <c r="AF55" t="n">
         <v>0.1739</v>
@@ -13569,10 +13569,10 @@
         <v>2.1198</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.0599</v>
+        <v>0.2718</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.2557</v>
+        <v>3.0438</v>
       </c>
       <c r="BE55" t="n">
         <v>1.7393</v>
@@ -13652,10 +13652,10 @@
         <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="F56" t="n">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="G56" t="n">
         <v>189</v>
@@ -13727,10 +13727,10 @@
         <v>0.1213</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.2831</v>
+        <v>0.0784</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.5182</v>
+        <v>0.7229</v>
       </c>
       <c r="AF56" t="n">
         <v>0.4777</v>
@@ -13802,10 +13802,10 @@
         <v>1.2133</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.8311</v>
+        <v>0.7836</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.1819</v>
+        <v>7.2293</v>
       </c>
       <c r="BE56" t="n">
         <v>4.7774</v>
@@ -13885,10 +13885,10 @@
         <v>17</v>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G57" t="n">
         <v>21</v>
@@ -13960,10 +13960,10 @@
         <v>0.0927</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.0818</v>
+        <v>0.0327</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.1309</v>
+        <v>0.18</v>
       </c>
       <c r="AF57" t="n">
         <v>0.1146</v>
@@ -14035,10 +14035,10 @@
         <v>0.9275</v>
       </c>
       <c r="BC57" t="n">
-        <v>0.8184</v>
+        <v>0.3274</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.3094</v>
+        <v>1.8004</v>
       </c>
       <c r="BE57" t="n">
         <v>1.1457</v>
@@ -14118,10 +14118,10 @@
         <v>27</v>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G58" t="n">
         <v>86</v>
@@ -14193,10 +14193,10 @@
         <v>0.1783</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.1321</v>
+        <v>0.0528</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.2642</v>
+        <v>0.3434</v>
       </c>
       <c r="AF58" t="n">
         <v>0.568</v>
@@ -14268,10 +14268,10 @@
         <v>1.7831</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.3208</v>
+        <v>0.5283</v>
       </c>
       <c r="BD58" t="n">
-        <v>2.6417</v>
+        <v>3.4342</v>
       </c>
       <c r="BE58" t="n">
         <v>5.6796</v>
@@ -14351,10 +14351,10 @@
         <v>101</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G59" t="n">
         <v>10</v>
@@ -14426,10 +14426,10 @@
         <v>0.5791</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.0344</v>
+        <v>0.0057</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.0745</v>
+        <v>0.1032</v>
       </c>
       <c r="AF59" t="n">
         <v>0.0573</v>
@@ -14501,10 +14501,10 @@
         <v>5.791</v>
       </c>
       <c r="BC59" t="n">
-        <v>0.344</v>
+        <v>0.0573</v>
       </c>
       <c r="BD59" t="n">
-        <v>0.7454</v>
+        <v>1.0321</v>
       </c>
       <c r="BE59" t="n">
         <v>0.5734</v>
@@ -14584,10 +14584,10 @@
         <v>60</v>
       </c>
       <c r="E60" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F60" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G60" t="n">
         <v>25</v>
@@ -14659,10 +14659,10 @@
         <v>0.1579</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.071</v>
+        <v>0.021</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.0684</v>
+        <v>0.1184</v>
       </c>
       <c r="AF60" t="n">
         <v>0.0658</v>
@@ -14734,10 +14734,10 @@
         <v>1.5785</v>
       </c>
       <c r="BC60" t="n">
-        <v>0.7103</v>
+        <v>0.2105</v>
       </c>
       <c r="BD60" t="n">
-        <v>0.684</v>
+        <v>1.1839</v>
       </c>
       <c r="BE60" t="n">
         <v>0.6577</v>
@@ -14817,10 +14817,10 @@
         <v>83</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G61" t="n">
         <v>12</v>
@@ -14892,10 +14892,10 @@
         <v>0.4742</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.0114</v>
+        <v>0.0057</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.08</v>
+        <v>0.0857</v>
       </c>
       <c r="AF61" t="n">
         <v>0.0686</v>
@@ -14967,10 +14967,10 @@
         <v>4.742</v>
       </c>
       <c r="BC61" t="n">
-        <v>0.1143</v>
+        <v>0.0571</v>
       </c>
       <c r="BD61" t="n">
-        <v>0.7999</v>
+        <v>0.857</v>
       </c>
       <c r="BE61" t="n">
         <v>0.6856</v>
@@ -15050,10 +15050,10 @@
         <v>101</v>
       </c>
       <c r="E62" t="n">
-        <v>204</v>
+        <v>64</v>
       </c>
       <c r="F62" t="n">
-        <v>317</v>
+        <v>457</v>
       </c>
       <c r="G62" t="n">
         <v>305</v>
@@ -15125,10 +15125,10 @@
         <v>0.1796</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.3627</v>
+        <v>0.1138</v>
       </c>
       <c r="AE62" t="n">
-        <v>0.5636</v>
+        <v>0.8125</v>
       </c>
       <c r="AF62" t="n">
         <v>0.5423</v>
@@ -15200,10 +15200,10 @@
         <v>1.7957</v>
       </c>
       <c r="BC62" t="n">
-        <v>3.627</v>
+        <v>1.1379</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.6361</v>
+        <v>8.1252</v>
       </c>
       <c r="BE62" t="n">
         <v>5.4227</v>
@@ -15283,10 +15283,10 @@
         <v>47</v>
       </c>
       <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
         <v>1</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -15358,10 +15358,10 @@
         <v>0.1505</v>
       </c>
       <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>0.0032</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
       </c>
       <c r="AF63" t="n">
         <v>0.0064</v>
@@ -15433,10 +15433,10 @@
         <v>1.5047</v>
       </c>
       <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="n">
         <v>0.032</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>0</v>
       </c>
       <c r="BE63" t="n">
         <v>0.064</v>
@@ -15516,10 +15516,10 @@
         <v>210</v>
       </c>
       <c r="E64" t="n">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="F64" t="n">
-        <v>518</v>
+        <v>696</v>
       </c>
       <c r="G64" t="n">
         <v>426</v>
@@ -15591,10 +15591,10 @@
         <v>0.2319</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.3192</v>
+        <v>0.1226</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.5721</v>
+        <v>0.7687</v>
       </c>
       <c r="AF64" t="n">
         <v>0.4705</v>
@@ -15666,10 +15666,10 @@
         <v>2.3193</v>
       </c>
       <c r="BC64" t="n">
-        <v>3.1917</v>
+        <v>1.2259</v>
       </c>
       <c r="BD64" t="n">
-        <v>5.7208</v>
+        <v>7.6867</v>
       </c>
       <c r="BE64" t="n">
         <v>4.7048</v>
@@ -15749,10 +15749,10 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G65" t="n">
         <v>13</v>
@@ -15824,10 +15824,10 @@
         <v>0.0462</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.0554</v>
+        <v>0.0185</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.1754</v>
+        <v>0.2124</v>
       </c>
       <c r="AF65" t="n">
         <v>0.12</v>
@@ -15899,10 +15899,10 @@
         <v>0.4617</v>
       </c>
       <c r="BC65" t="n">
-        <v>0.554</v>
+        <v>0.1847</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.7544</v>
+        <v>2.1237</v>
       </c>
       <c r="BE65" t="n">
         <v>1.2004</v>
@@ -15982,10 +15982,10 @@
         <v>90</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G66" t="n">
         <v>32</v>
@@ -16057,10 +16057,10 @@
         <v>0.7648</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.0935</v>
+        <v>0.0085</v>
       </c>
       <c r="AE66" t="n">
-        <v>0.2464</v>
+        <v>0.3314</v>
       </c>
       <c r="AF66" t="n">
         <v>0.2719</v>
@@ -16132,10 +16132,10 @@
         <v>7.6479</v>
       </c>
       <c r="BC66" t="n">
-        <v>0.9347</v>
+        <v>0.085</v>
       </c>
       <c r="BD66" t="n">
-        <v>2.4643</v>
+        <v>3.3141</v>
       </c>
       <c r="BE66" t="n">
         <v>2.7192</v>
@@ -16215,10 +16215,10 @@
         <v>274</v>
       </c>
       <c r="E67" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="F67" t="n">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="G67" t="n">
         <v>153</v>
@@ -16290,10 +16290,10 @@
         <v>0.497</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.1251</v>
+        <v>0.0381</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.3029</v>
+        <v>0.39</v>
       </c>
       <c r="AF67" t="n">
         <v>0.2775</v>
@@ -16365,10 +16365,10 @@
         <v>4.9697</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.2515</v>
+        <v>0.3809</v>
       </c>
       <c r="BD67" t="n">
-        <v>3.029</v>
+        <v>3.8996</v>
       </c>
       <c r="BE67" t="n">
         <v>2.7751</v>
@@ -16448,10 +16448,10 @@
         <v>33</v>
       </c>
       <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
         <v>2</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>4</v>
@@ -16523,10 +16523,10 @@
         <v>0.2301</v>
       </c>
       <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
         <v>0.0139</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
       </c>
       <c r="AF68" t="n">
         <v>0.0279</v>
@@ -16598,10 +16598,10 @@
         <v>2.3013</v>
       </c>
       <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
         <v>0.1395</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>0</v>
       </c>
       <c r="BE68" t="n">
         <v>0.2789</v>
@@ -16681,10 +16681,10 @@
         <v>275</v>
       </c>
       <c r="E69" t="n">
-        <v>423</v>
+        <v>166</v>
       </c>
       <c r="F69" t="n">
-        <v>1386</v>
+        <v>1643</v>
       </c>
       <c r="G69" t="n">
         <v>753</v>
@@ -16756,10 +16756,10 @@
         <v>0.1634</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.2513</v>
+        <v>0.0986</v>
       </c>
       <c r="AE69" t="n">
-        <v>0.8235</v>
+        <v>0.9762</v>
       </c>
       <c r="AF69" t="n">
         <v>0.4474</v>
@@ -16831,10 +16831,10 @@
         <v>1.634</v>
       </c>
       <c r="BC69" t="n">
-        <v>2.5133</v>
+        <v>0.9863</v>
       </c>
       <c r="BD69" t="n">
-        <v>8.2352</v>
+        <v>9.7622</v>
       </c>
       <c r="BE69" t="n">
         <v>4.4741</v>
@@ -16914,10 +16914,10 @@
         <v>46</v>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="F70" t="n">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="G70" t="n">
         <v>60</v>
@@ -16989,10 +16989,10 @@
         <v>0.2413</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.278</v>
+        <v>0.0996</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.5979</v>
+        <v>0.7762</v>
       </c>
       <c r="AF70" t="n">
         <v>0.3147</v>
@@ -17064,10 +17064,10 @@
         <v>2.4125</v>
       </c>
       <c r="BC70" t="n">
-        <v>2.7797</v>
+        <v>0.9965</v>
       </c>
       <c r="BD70" t="n">
-        <v>5.9789</v>
+        <v>7.7621</v>
       </c>
       <c r="BE70" t="n">
         <v>3.1468</v>
@@ -17380,10 +17380,10 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G72" t="n">
         <v>52</v>
@@ -17455,10 +17455,10 @@
         <v>0.063</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.3419</v>
+        <v>0.135</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.3779</v>
+        <v>0.5849</v>
       </c>
       <c r="AF72" t="n">
         <v>0.4679</v>
@@ -17530,10 +17530,10 @@
         <v>0.6299</v>
       </c>
       <c r="BC72" t="n">
-        <v>3.4194</v>
+        <v>1.3498</v>
       </c>
       <c r="BD72" t="n">
-        <v>3.7794</v>
+        <v>5.849</v>
       </c>
       <c r="BE72" t="n">
         <v>4.6792</v>
@@ -17613,10 +17613,10 @@
         <v>118</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -17688,10 +17688,10 @@
         <v>0.3128</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.0106</v>
+        <v>0.0027</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.0159</v>
+        <v>0.0239</v>
       </c>
       <c r="AF73" t="n">
         <v>0.0053</v>
@@ -17763,10 +17763,10 @@
         <v>3.1281</v>
       </c>
       <c r="BC73" t="n">
-        <v>0.106</v>
+        <v>0.0265</v>
       </c>
       <c r="BD73" t="n">
-        <v>0.1591</v>
+        <v>0.2386</v>
       </c>
       <c r="BE73" t="n">
         <v>0.053</v>
@@ -17846,10 +17846,10 @@
         <v>85</v>
       </c>
       <c r="E74" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="G74" t="n">
         <v>94</v>
@@ -17921,10 +17921,10 @@
         <v>0.2969</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.1956</v>
+        <v>0.0384</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.4646</v>
+        <v>0.6218</v>
       </c>
       <c r="AF74" t="n">
         <v>0.3284</v>
@@ -17996,10 +17996,10 @@
         <v>2.9693</v>
       </c>
       <c r="BC74" t="n">
-        <v>1.9563</v>
+        <v>0.3843</v>
       </c>
       <c r="BD74" t="n">
-        <v>4.6461</v>
+        <v>6.2181</v>
       </c>
       <c r="BE74" t="n">
         <v>3.2837</v>
@@ -18079,10 +18079,10 @@
         <v>103</v>
       </c>
       <c r="E75" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
         <v>55</v>
@@ -18154,10 +18154,10 @@
         <v>0.4822</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.1685</v>
+        <v>0.0702</v>
       </c>
       <c r="AE75" t="n">
-        <v>0.3698</v>
+        <v>0.4681</v>
       </c>
       <c r="AF75" t="n">
         <v>0.2575</v>
@@ -18229,10 +18229,10 @@
         <v>4.8216</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.6852</v>
+        <v>0.7022</v>
       </c>
       <c r="BD75" t="n">
-        <v>3.6982</v>
+        <v>4.6812</v>
       </c>
       <c r="BE75" t="n">
         <v>2.5747</v>
@@ -18312,10 +18312,10 @@
         <v>289</v>
       </c>
       <c r="E76" t="n">
-        <v>465</v>
+        <v>149</v>
       </c>
       <c r="F76" t="n">
-        <v>770</v>
+        <v>1086</v>
       </c>
       <c r="G76" t="n">
         <v>785</v>
@@ -18387,10 +18387,10 @@
         <v>0.2511</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.404</v>
+        <v>0.1294</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.6689</v>
+        <v>0.9435</v>
       </c>
       <c r="AF76" t="n">
         <v>0.682</v>
@@ -18462,10 +18462,10 @@
         <v>2.5107</v>
       </c>
       <c r="BC76" t="n">
-        <v>4.0397</v>
+        <v>1.2944</v>
       </c>
       <c r="BD76" t="n">
-        <v>6.6894</v>
+        <v>9.4347</v>
       </c>
       <c r="BE76" t="n">
         <v>6.8197</v>
@@ -18545,10 +18545,10 @@
         <v>419</v>
       </c>
       <c r="E77" t="n">
-        <v>1055</v>
+        <v>330</v>
       </c>
       <c r="F77" t="n">
-        <v>1607</v>
+        <v>2332</v>
       </c>
       <c r="G77" t="n">
         <v>1637</v>
@@ -18620,10 +18620,10 @@
         <v>0.2489</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.6266</v>
+        <v>0.196</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.9545</v>
+        <v>1.3851</v>
       </c>
       <c r="AF77" t="n">
         <v>0.9723</v>
@@ -18695,10 +18695,10 @@
         <v>2.4886</v>
       </c>
       <c r="BC77" t="n">
-        <v>6.266</v>
+        <v>1.96</v>
       </c>
       <c r="BD77" t="n">
-        <v>9.5445</v>
+        <v>13.8505</v>
       </c>
       <c r="BE77" t="n">
         <v>9.7227</v>
@@ -18778,10 +18778,10 @@
         <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F78" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G78" t="n">
         <v>45</v>
@@ -18853,10 +18853,10 @@
         <v>0.2302</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.1995</v>
+        <v>0.0844</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.3223</v>
+        <v>0.4374</v>
       </c>
       <c r="AF78" t="n">
         <v>0.3453</v>
@@ -18928,10 +18928,10 @@
         <v>2.302</v>
       </c>
       <c r="BC78" t="n">
-        <v>1.9951</v>
+        <v>0.8441</v>
       </c>
       <c r="BD78" t="n">
-        <v>3.2228</v>
+        <v>4.3738</v>
       </c>
       <c r="BE78" t="n">
         <v>3.453</v>
@@ -19244,10 +19244,10 @@
         <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -19319,10 +19319,10 @@
         <v>0.0998</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.0143</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.0285</v>
+        <v>0.0428</v>
       </c>
       <c r="AF80" t="n">
         <v>0</v>
@@ -19394,10 +19394,10 @@
         <v>0.9979</v>
       </c>
       <c r="BC80" t="n">
-        <v>0.1426</v>
+        <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>0.2851</v>
+        <v>0.4277</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -19710,10 +19710,10 @@
         <v>64</v>
       </c>
       <c r="E82" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="G82" t="n">
         <v>45</v>
@@ -19785,10 +19785,10 @@
         <v>0.1677</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.1625</v>
+        <v>0.0472</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.2097</v>
+        <v>0.325</v>
       </c>
       <c r="AF82" t="n">
         <v>0.1179</v>
@@ -19860,10 +19860,10 @@
         <v>1.6774</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.625</v>
+        <v>0.4718</v>
       </c>
       <c r="BD82" t="n">
-        <v>2.0967</v>
+        <v>3.2499</v>
       </c>
       <c r="BE82" t="n">
         <v>1.1794</v>
@@ -19943,10 +19943,10 @@
         <v>64</v>
       </c>
       <c r="E83" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F83" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="G83" t="n">
         <v>99</v>
@@ -20018,10 +20018,10 @@
         <v>0.2985</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.3031</v>
+        <v>0.1166</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.3871</v>
+        <v>0.5736</v>
       </c>
       <c r="AF83" t="n">
         <v>0.4617</v>
@@ -20093,10 +20093,10 @@
         <v>2.9847</v>
       </c>
       <c r="BC83" t="n">
-        <v>3.0313</v>
+        <v>1.1659</v>
       </c>
       <c r="BD83" t="n">
-        <v>3.8707</v>
+        <v>5.7361</v>
       </c>
       <c r="BE83" t="n">
         <v>4.6169</v>
@@ -20176,10 +20176,10 @@
         <v>87</v>
       </c>
       <c r="E84" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="F84" t="n">
-        <v>363</v>
+        <v>440</v>
       </c>
       <c r="G84" t="n">
         <v>317</v>
@@ -20251,10 +20251,10 @@
         <v>0.1502</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.209</v>
+        <v>0.076</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.6269</v>
+        <v>0.7599</v>
       </c>
       <c r="AF84" t="n">
         <v>0.5474</v>
@@ -20326,10 +20326,10 @@
         <v>1.5024</v>
       </c>
       <c r="BC84" t="n">
-        <v>2.0896</v>
+        <v>0.7599</v>
       </c>
       <c r="BD84" t="n">
-        <v>6.2688</v>
+        <v>7.5985</v>
       </c>
       <c r="BE84" t="n">
         <v>5.4744</v>
@@ -20409,10 +20409,10 @@
         <v>38</v>
       </c>
       <c r="E85" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F85" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="G85" t="n">
         <v>41</v>
@@ -20484,10 +20484,10 @@
         <v>0.0952</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.1027</v>
+        <v>0.0401</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.1753</v>
+        <v>0.2379</v>
       </c>
       <c r="AF85" t="n">
         <v>0.1027</v>
@@ -20559,10 +20559,10 @@
         <v>0.9517</v>
       </c>
       <c r="BC85" t="n">
-        <v>1.0269</v>
+        <v>0.4007</v>
       </c>
       <c r="BD85" t="n">
-        <v>1.7532</v>
+        <v>2.3793</v>
       </c>
       <c r="BE85" t="n">
         <v>1.0269</v>
